--- a/analisi_dati_ml.xlsx
+++ b/analisi_dati_ml.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\novel\OneDrive\Desktop\metodi_computazionali\ml_digits_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C581FFA-9AA2-4843-94F9-CD7718342DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9657E0DE-ADF8-4397-A021-8CC4B1E63F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8103CB19-A3F3-4DFE-8059-7DCAE84888A7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="47">
   <si>
     <t>Modello</t>
   </si>
@@ -155,22 +155,28 @@
     <t>115s</t>
   </si>
   <si>
-    <t>c.a 50s</t>
-  </si>
-  <si>
     <t>1019s</t>
   </si>
   <si>
     <t>CNN</t>
   </si>
   <si>
-    <t>1555s</t>
-  </si>
-  <si>
     <t>1s  GPU</t>
   </si>
   <si>
     <t>230s GPU</t>
+  </si>
+  <si>
+    <t>1555s - 45s GPU</t>
+  </si>
+  <si>
+    <t>overfitting after 40 epochs</t>
+  </si>
+  <si>
+    <t>84s GPU</t>
+  </si>
+  <si>
+    <t>92s GPU</t>
   </si>
 </sst>
 </file>
@@ -685,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39320CA-571A-4942-9273-334A6AAB44AB}">
-  <dimension ref="B2:O25"/>
+  <dimension ref="B2:P25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.1796875" customWidth="1"/>
@@ -700,10 +706,11 @@
     <col min="11" max="11" width="10.6328125" customWidth="1"/>
     <col min="12" max="12" width="15.453125" customWidth="1"/>
     <col min="13" max="13" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" ht="16" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -718,7 +725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
@@ -757,7 +764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
@@ -796,7 +803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
@@ -835,7 +842,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
@@ -874,7 +881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -913,7 +920,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
@@ -952,7 +959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
@@ -993,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
@@ -1025,19 +1032,19 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>0.97099999999999997</v>
+        <v>0.99239999999999995</v>
       </c>
       <c r="M10" s="3">
-        <v>0.95599999999999996</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1069,21 +1076,24 @@
         <v>100</v>
       </c>
       <c r="L11" s="3">
-        <v>0.99099999999999999</v>
+        <v>0.99970000000000003</v>
       </c>
       <c r="M11" s="3">
-        <v>0.96060000000000001</v>
+        <v>0.96540000000000004</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="O11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1">
         <v>1E-3</v>
@@ -1098,11 +1108,11 @@
         <v>0.98819999999999997</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" s="1">
         <v>1E-3</v>
@@ -1117,10 +1127,10 @@
         <v>0.99099999999999999</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1135,7 +1145,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1150,7 +1160,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="2:15" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="16" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>1</v>
       </c>
@@ -1169,7 +1179,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +1385,7 @@
         <v>0.98640000000000005</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>33</v>
@@ -1418,7 +1428,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="1">
         <v>1E-3</v>
@@ -1433,7 +1443,7 @@
         <v>0.99570000000000003</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1454,23 +1464,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5faecb7a-220e-4e2d-8715-f86974b44aaf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010012F057B85285B6468AAABCE0FB0E27BB" ma:contentTypeVersion="6" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="d21193acf438d5c7fb70704988d81320">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5faecb7a-220e-4e2d-8715-f86974b44aaf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec854a3c3cbd78042c34559226770c78" ns3:_="">
     <xsd:import namespace="5faecb7a-220e-4e2d-8715-f86974b44aaf"/>
@@ -1626,31 +1619,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67235D91-75BC-4413-BCB6-9C5CEBA673F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="5faecb7a-220e-4e2d-8715-f86974b44aaf"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03638E86-EF67-4B8C-A94F-4F998F5E4C5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5faecb7a-220e-4e2d-8715-f86974b44aaf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB81D698-4A46-4E36-9597-5C45E2AABD02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1666,4 +1652,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03638E86-EF67-4B8C-A94F-4F998F5E4C5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67235D91-75BC-4413-BCB6-9C5CEBA673F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="5faecb7a-220e-4e2d-8715-f86974b44aaf"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>